--- a/FRI_Veh_Auth.xlsx
+++ b/FRI_Veh_Auth.xlsx
@@ -513,6 +513,46 @@
         <v>0.0001266002655029297</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KAF91EA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9WMNQWB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0001542568206787109</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KAF91EA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>I47CW87</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8170</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0001215934753417969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
